--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318213</v>
       </c>
       <c r="B2" t="n">
-        <v>97964</v>
+        <v>97967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132318212</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>97966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318213</v>
       </c>
       <c r="B2" t="n">
-        <v>97967</v>
+        <v>97975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132318212</v>
       </c>
       <c r="B3" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318213</v>
       </c>
       <c r="B2" t="n">
-        <v>97975</v>
+        <v>97985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132318212</v>
       </c>
       <c r="B3" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318213</v>
       </c>
       <c r="B2" t="n">
-        <v>97985</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132318212</v>
       </c>
       <c r="B3" t="n">
-        <v>97984</v>
+        <v>97985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318213</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>132318212</v>
       </c>
       <c r="B3" t="n">
-        <v>97985</v>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132318213</v>
+        <v>132318212</v>
       </c>
       <c r="B2" t="n">
-        <v>97994</v>
+        <v>98063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,22 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224364</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -710,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636391</v>
+        <v>636371</v>
       </c>
       <c r="R2" t="n">
-        <v>6564125</v>
+        <v>6564142</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -740,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132318212</v>
+        <v>132318213</v>
       </c>
       <c r="B3" t="n">
-        <v>97993</v>
+        <v>98064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,26 +792,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>224364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636371</v>
+        <v>636391</v>
       </c>
       <c r="R3" t="n">
-        <v>6564142</v>
+        <v>6564125</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -846,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 17009-2026 artfynd.xlsx
+++ b/artfynd/A 17009-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318212</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132318213</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>